--- a/output/pdf_financials_xlsx/HAN.xlsx
+++ b/output/pdf_financials_xlsx/HAN.xlsx
@@ -5896,43 +5896,43 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.285241</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.285241</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.285241</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.311839</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.471043</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.632469</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.709194</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.276541</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.338292</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.307777</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.966037</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.758975</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.447227</v>
       </c>
     </row>
     <row r="93">
@@ -10034,7 +10034,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -17546,7 +17550,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -18416,7 +18424,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19274,7 +19286,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19848,7 +19864,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HAN.xlsx
+++ b/output/pdf_financials_xlsx/HAN.xlsx
@@ -1096,25 +1096,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.004219</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.021922</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.011369</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.008959</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.010911</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -2161,25 +2161,25 @@
         <v>-0.200111</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.200111</v>
+        <v>-0.200885</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.150416</v>
+        <v>-0.151025</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.679942</v>
+        <v>-0.684161</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.113902</v>
+        <v>-1.135824</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.020444</v>
+        <v>-1.031813</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.164134</v>
+        <v>-1.173093</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.593809</v>
+        <v>-1.60472</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2291,25 +2291,25 @@
         <v>-0.200111</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.200111</v>
+        <v>-0.200885</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.150416</v>
+        <v>-0.151025</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.679942</v>
+        <v>-0.684161</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.113902</v>
+        <v>-1.135824</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.020444</v>
+        <v>-1.031813</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.164134</v>
+        <v>-1.173093</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.593809</v>
+        <v>-1.60472</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2585,52 +2585,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.653697</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.246075</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.042438</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000554</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.05467</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07541</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.039752</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.172836</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.477866</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.371663</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.690911</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.799811</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.37685</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.318801</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.945438</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.273267</v>
       </c>
     </row>
     <row r="35">
@@ -2695,52 +2695,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.653697</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.246075</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.042438</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000554</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.05467</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07541</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.039752</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.172836</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.477866</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.371663</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.690911</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.799811</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.37685</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.318801</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.945438</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.273267</v>
       </c>
     </row>
     <row r="37">
@@ -3355,52 +3355,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.660589</v>
+        <v>0.006892</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.251108</v>
+        <v>0.005033</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.052281</v>
+        <v>0.009842999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.003587</v>
+        <v>0.003033</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.05857</v>
+        <v>0.0039</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08431</v>
+        <v>0.0089</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.043652</v>
+        <v>0.0039</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.272155</v>
+        <v>0.099319</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.526176</v>
+        <v>0.04831</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.42116</v>
+        <v>0.049497</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.78596</v>
+        <v>0.09504899999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.888325</v>
+        <v>0.088514</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.44021</v>
+        <v>0.06336</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.440298</v>
+        <v>0.121497</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.063012</v>
+        <v>0.117574</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.611023</v>
+        <v>0.337756</v>
       </c>
     </row>
     <row r="49">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -29542,7 +29542,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
